--- a/data/JM_history.xlsx
+++ b/data/JM_history.xlsx
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026 — This monitor</t>
+          <t>2026 — This monitor (v13)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1. Removed the outlier clip (model-structure change).&lt;br&gt;2. Added masked recovery (volume) features.&lt;br&gt;3. Added unconditional intraday close-location-value features.&lt;br&gt;4. Added the flip-risk signal (bear-proximity traffic light).&lt;br&gt;5. Added signal confirmation - a flip publishes only after persisting 2 days (to bear) / 3 days (to bull), keeping 1-2-day whipsaws out of the signal.&lt;br&gt;6. Added a bear-entry conviction veto (v5) - a bear flip also needs the model&amp;#39;s own bear-probability &amp;gt;= 60%, holding back low-conviction alarms that are historically false.&lt;br&gt;7. Added an 8-trading-day minimum hold (v6) - a published signal never reverses in under 8 trading days; a pending reversal shows as elevated flip-risk on a stable signal instead.&lt;br&gt;Result: capture improves from 1.16x to 3.41x of buy-and-hold on NDX.</t>
+          <t>The published monitor is &lt;b&gt;two models&lt;/b&gt;, one per market, each market assigned the one that measurably defends it better.&lt;br&gt;&lt;b&gt;1. Feature set rebuilt&lt;/b&gt; (v11) - 21 raw price/volume features, no outlier clip and &lt;i&gt;no masking&lt;/i&gt;: every feature speaks every day. The three trend features carry 70% of the distance metric.&lt;br&gt;&lt;b&gt;2. Decode simplified&lt;/b&gt; (v11) - only the 2-day/3-day confirmation survives. The v5 conviction veto and the v6 eight-day minimum hold were both &lt;b&gt;removed&lt;/b&gt;: measured across 11 markets the hold was the harmful half of the decode.&lt;br&gt;&lt;b&gt;3. Flip-risk signal&lt;/b&gt; - the bear-proximity traffic light shown on every tab.&lt;br&gt;&lt;b&gt;4. Second model added&lt;/b&gt; (v13) - the Volatility Model, previously used only as a confidence input, now drives the decision alone on markets where the jump model cannot defend. Assignment is by rule, not by hand: a market switches only if the jump model fails a re-timing test &lt;i&gt;and&lt;/i&gt; the Volatility Model detects its bears better.&lt;br&gt;&lt;b&gt;5. Markets screened out&lt;/b&gt; (v13) - HSCEI was removed: no approach tested detects its bear markets.&lt;br&gt;&lt;b&gt;What it is for:&lt;/b&gt; protection survives a re-timing test on 5 of the 6 indexes shown; total return does not improve except on NDX. Read this as a &lt;b&gt;drawdown-reduction&lt;/b&gt; tool.</t>
         </is>
       </c>
     </row>
